--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69E5C8ED-37AC-4491-857D-C00897A3A21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23AFF275-5B73-484C-ABD9-EFDED758CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="94">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -294,9 +320,6 @@
     <t>UCE_max nuclear capacity</t>
   </si>
   <si>
-    <t>UC_RHSRT~2050</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -357,6 +380,15 @@
     <t>wind*</t>
   </si>
   <si>
+    <t>~UC_T: 2050</t>
+  </si>
+  <si>
+    <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -382,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,8 +464,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +498,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -480,13 +533,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -497,10 +551,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -947,15 +1004,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.41793910173855464</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -977,7 +1031,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -987,7 +1041,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1006,7 +1060,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1244,7 +1298,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1257,7 +1311,7 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3">
         <v>0.14894542291802565</v>
@@ -1277,7 +1331,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -1317,9 +1371,6 @@
       <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -1333,7 +1384,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
         <v>64</v>
@@ -1345,15 +1396,18 @@
         <v>1</v>
       </c>
       <c r="AB15">
+        <f>AE15*2.5</f>
+        <v>138.82499999999999</v>
+      </c>
+      <c r="AC15">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="11">
         <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
         <v>55.53</v>
       </c>
-      <c r="AC15">
-        <v>3</v>
-      </c>
-      <c r="AD15">
-        <f>AB15*2.5</f>
-        <v>138.82499999999999</v>
+      <c r="AF15" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -1495,24 +1549,24 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
@@ -1575,7 +1629,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -1583,7 +1637,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1606,41 +1661,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11">
         <v>70</v>
@@ -1674,7 +1729,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1682,16 +1737,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -1716,7 +1771,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1746,7 +1801,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1776,7 +1831,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1806,7 +1861,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1947,7 +2002,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B9">
         <v>2000</v>
@@ -2059,7 +2114,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B17">
         <v>2001</v>
@@ -2171,7 +2226,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B25">
         <v>2002</v>
@@ -2283,7 +2338,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B33">
         <v>2003</v>
@@ -2395,7 +2450,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41">
         <v>2004</v>
@@ -2507,7 +2562,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B49">
         <v>2005</v>
@@ -2619,7 +2674,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B57">
         <v>2006</v>
@@ -2731,7 +2786,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B65">
         <v>2007</v>
@@ -2843,7 +2898,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B73">
         <v>2008</v>
@@ -2955,7 +3010,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B81">
         <v>2009</v>
@@ -3067,7 +3122,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B89">
         <v>2010</v>
@@ -3179,7 +3234,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B97">
         <v>2011</v>
@@ -3291,7 +3346,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B105">
         <v>2012</v>
@@ -3403,7 +3458,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B113">
         <v>2013</v>
@@ -3515,7 +3570,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B121">
         <v>2014</v>
@@ -3627,7 +3682,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B129">
         <v>2015</v>
@@ -3739,7 +3794,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B137">
         <v>2016</v>
@@ -3851,7 +3906,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B145">
         <v>2017</v>
@@ -3963,7 +4018,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B153">
         <v>2018</v>
@@ -4075,7 +4130,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B161">
         <v>2019</v>
@@ -4187,7 +4242,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B169">
         <v>2020</v>
@@ -4299,7 +4354,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B177">
         <v>2021</v>
@@ -4411,7 +4466,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -4523,7 +4578,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B193">
         <v>2023</v>
@@ -4635,7 +4690,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B201">
         <v>2000</v>
@@ -4747,7 +4802,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B209">
         <v>2001</v>
@@ -4859,7 +4914,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B217">
         <v>2002</v>
@@ -4971,7 +5026,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B225">
         <v>2003</v>
@@ -5083,7 +5138,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B233">
         <v>2004</v>
@@ -5195,7 +5250,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B241">
         <v>2005</v>
@@ -5307,7 +5362,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B249">
         <v>2006</v>
@@ -5419,7 +5474,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B257">
         <v>2007</v>
@@ -5531,7 +5586,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B265">
         <v>2008</v>
@@ -5643,7 +5698,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B273">
         <v>2009</v>
@@ -5755,7 +5810,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B281">
         <v>2010</v>
@@ -5867,7 +5922,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B289">
         <v>2011</v>
@@ -5979,7 +6034,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B297">
         <v>2012</v>
@@ -6091,7 +6146,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B305">
         <v>2013</v>
@@ -6203,7 +6258,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B313">
         <v>2014</v>
@@ -6315,7 +6370,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B321">
         <v>2015</v>
@@ -6427,7 +6482,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B329">
         <v>2016</v>
@@ -6539,7 +6594,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B337">
         <v>2017</v>
@@ -6651,7 +6706,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B345">
         <v>2018</v>
@@ -6763,7 +6818,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B353">
         <v>2019</v>
@@ -6875,7 +6930,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B361">
         <v>2020</v>
@@ -6987,7 +7042,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B369">
         <v>2021</v>
@@ -7099,7 +7154,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B377">
         <v>2022</v>
@@ -7211,7 +7266,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B385">
         <v>2023</v>
@@ -7323,7 +7378,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B393">
         <v>2000</v>
@@ -7435,7 +7490,7 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B401">
         <v>2001</v>
@@ -7547,7 +7602,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B409">
         <v>2002</v>
@@ -7659,7 +7714,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B417">
         <v>2003</v>
@@ -7771,7 +7826,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B425">
         <v>2004</v>
@@ -7883,7 +7938,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B433">
         <v>2005</v>
@@ -7995,7 +8050,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B441">
         <v>2006</v>
@@ -8107,7 +8162,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B449">
         <v>2007</v>
@@ -8219,7 +8274,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B457">
         <v>2008</v>
@@ -8331,7 +8386,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B465">
         <v>2009</v>
@@ -8443,7 +8498,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B473">
         <v>2010</v>
@@ -8555,7 +8610,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B481">
         <v>2011</v>
@@ -8667,7 +8722,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B489">
         <v>2012</v>
@@ -8779,7 +8834,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B497">
         <v>2013</v>
@@ -8891,7 +8946,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B505">
         <v>2014</v>
@@ -9003,7 +9058,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B513">
         <v>2015</v>
@@ -9115,7 +9170,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B521">
         <v>2016</v>
@@ -9227,7 +9282,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B529">
         <v>2017</v>
@@ -9339,7 +9394,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B537">
         <v>2018</v>
@@ -9451,7 +9506,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B545">
         <v>2019</v>
@@ -9563,7 +9618,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B553">
         <v>2020</v>
@@ -9675,7 +9730,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B561">
         <v>2021</v>
@@ -9787,7 +9842,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B569">
         <v>2022</v>
@@ -9899,7 +9954,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B577">
         <v>2023</v>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23AFF275-5B73-484C-ABD9-EFDED758CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1DFF262-DEB1-4107-980B-AA5A100B732E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1DFF262-DEB1-4107-980B-AA5A100B732E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14ED7A13-CBB2-4FD1-8E07-52E2A2C93D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14ED7A13-CBB2-4FD1-8E07-52E2A2C93D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C74D6D-C369-4A35-BEC1-E3C29DF73D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C74D6D-C369-4A35-BEC1-E3C29DF73D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0141DCBA-4344-4112-942A-D565D773CE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0141DCBA-4344-4112-942A-D565D773CE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07CF8680-F2D4-4A0D-8DF7-BE8D902D384C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07CF8680-F2D4-4A0D-8DF7-BE8D902D384C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A4C66AE-8F99-48DC-8055-FEFE9FA66660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A4C66AE-8F99-48DC-8055-FEFE9FA66660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46F88209-2240-4412-B9E4-F85AE636B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46F88209-2240-4412-B9E4-F85AE636B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5211D22D-2CD3-4CA3-9969-D9052ACEB061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5211D22D-2CD3-4CA3-9969-D9052ACEB061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D4E13A-54B4-4A67-B3A7-D3B0ED79065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D4E13A-54B4-4A67-B3A7-D3B0ED79065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17C890B1-A9FF-4795-B51F-F13D97AFC508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17C890B1-A9FF-4795-B51F-F13D97AFC508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AF80ECA-0D44-4E46-A921-ED3CBE183E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AF80ECA-0D44-4E46-A921-ED3CBE183E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B5E3185-FF33-4499-B026-C5BEA9428CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B5E3185-FF33-4499-B026-C5BEA9428CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F72DA9F-F08B-4748-BC18-363E92E32A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F72DA9F-F08B-4748-BC18-363E92E32A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1408CF67-FCFC-4690-8F8B-410173988A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1408CF67-FCFC-4690-8F8B-410173988A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43A55DF9-87CC-48E3-A640-58B43C483802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43A55DF9-87CC-48E3-A640-58B43C483802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2C66469-9A2C-4304-AA49-251521AE8106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="buildrates" sheetId="4" r:id="rId2"/>
-    <sheet name="historical_data_long" sheetId="3" r:id="rId3"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
+    <sheet name="buildrates" sheetId="4" r:id="rId3"/>
+    <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -123,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="129">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -396,6 +397,112 @@
   </si>
   <si>
     <t>windon</t>
+  </si>
+  <si>
+    <t>RE Targets from EMBER</t>
+  </si>
+  <si>
+    <t>TARGET_YEAR</t>
+  </si>
+  <si>
+    <t>FUEL_CATEGORY</t>
+  </si>
+  <si>
+    <t>METRIC</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>SOURCE_TYPE</t>
+  </si>
+  <si>
+    <t>SOURCE_NAME</t>
+  </si>
+  <si>
+    <t>PUBLISHER</t>
+  </si>
+  <si>
+    <t>ANNOUNCEMENT_DATE</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>SOURCE_SUMMARY</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>capacity_total_gw</t>
+  </si>
+  <si>
+    <t>Executive order</t>
+  </si>
+  <si>
+    <t>Announcement of China's 3rd Nationally Determined Contribution</t>
+  </si>
+  <si>
+    <t>Xi Jinping, President of the People's Republic of China</t>
+  </si>
+  <si>
+    <t>https://www.mfa.gov.cn/zyxw/202509/t20250925_11716488.shtml</t>
+  </si>
+  <si>
+    <t>Xi Jinping, President of the People's Republic of China announced the third Nationally Determined Contribution for China. In his speech he announced a series of 2035 targets. This includes an aim to reach economy-wide net  greenhouse gas emissions reduction of 7-10% from their peak and a non-fossil energy consumption to account for over 30% of total energy consumption. The total installed capacity of wind and solar power generation by 2035 will be more than six times the 2020 level, aiming to reach 3,600 GW.</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>Wind and solar</t>
+  </si>
+  <si>
+    <t>Official projections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中国2030年能源电力发展规划研究及2060年展望 (China's 2030 Energy and Power Development Planning Research and 2060 Outlook) </t>
+  </si>
+  <si>
+    <t>Global Energy Interconnection Development and Cooperation Organisation (GEIDO)</t>
+  </si>
+  <si>
+    <t>https://www.gei-journal.com/cn/wonderfulReportCn/20211209/1468969880752623616.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEIDO, a government-affiliated think-tank and chaired by the Chairman of State Grid Corporation of China and China Electricity Council, produced a study that projects power capacity development pathways for 2030 and onwards. President Xi's statement on renewable ambition and the 14th Five-Year Plan are incorporated into this study, including goals to peak emissions by 2030 and reach carbon neutrality by 2060. While results of this study is not an explicit target, they can provide an estimate for what China's ambition for 2030 may look like in their power sector planning.  The research suggests that clean power will account for 52.5% electricity consumption by 2030. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.21, table "The total installed capacity and structure of power supply fomr 2020 to 2060", machine-translated from Chinese.
+p. 21 "Clean energy power generation will be 5.8 trillion kwh, accounting for 52.5% of total electricity generation." </t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>share_of_generation_pct</t>
   </si>
   <si>
     <t>BUILD RATE ASSUMPTIONS</t>
@@ -540,7 +647,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -553,6 +660,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -890,6 +1001,525 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4862554F-AC20-4F16-B561-D693B5C461C5}">
+  <dimension ref="B9:L24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="12">
+        <v>45924</v>
+      </c>
+      <c r="J11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12">
+        <v>554</v>
+      </c>
+      <c r="F12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="12">
+        <v>45924</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="12">
+        <v>45924</v>
+      </c>
+      <c r="J13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="12">
+        <v>45924</v>
+      </c>
+      <c r="J14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15">
+        <v>2604</v>
+      </c>
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="12">
+        <v>45924</v>
+      </c>
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17">
+        <v>1050</v>
+      </c>
+      <c r="F17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J17" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18">
+        <v>185</v>
+      </c>
+      <c r="F18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J18" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19">
+        <v>554</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J19" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20">
+        <v>108</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K20" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21">
+        <v>1025</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J21" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22">
+        <v>130</v>
+      </c>
+      <c r="F22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J22" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23">
+        <v>800</v>
+      </c>
+      <c r="F23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J23" t="s">
+        <v>117</v>
+      </c>
+      <c r="K23" t="s">
+        <v>118</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24">
+        <v>52.5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="12">
+        <v>44256</v>
+      </c>
+      <c r="J24" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1642,7 +2272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A9:J23"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1661,12 +2291,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1695,7 +2325,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C11">
         <v>70</v>
@@ -1883,7 +2513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D625"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2C66469-9A2C-4304-AA49-251521AE8106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3609C7F-F1B1-49B2-B279-4723AF75BDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,10 +660,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -1004,513 +1002,537 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4862554F-AC20-4F16-B561-D693B5C461C5}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="65.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>91</v>
       </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
+      <c r="B10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11">
+      <c r="B11" s="12">
         <v>2030</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="12">
         <v>82</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <v>45924</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="12" t="s">
         <v>109</v>
       </c>
+      <c r="L11" s="12"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12">
+      <c r="B12" s="12">
         <v>2030</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="12">
         <v>554</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>45924</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="12" t="s">
         <v>109</v>
       </c>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B13">
+      <c r="B13" s="12">
         <v>2030</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F13" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>45924</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="12" t="s">
         <v>109</v>
       </c>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B14">
+      <c r="B14" s="12">
         <v>2030</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <v>45924</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="12" t="s">
         <v>109</v>
       </c>
+      <c r="L14" s="12"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B15">
+      <c r="B15" s="12">
         <v>2030</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="12">
         <v>2604</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <v>45924</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="12" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B16">
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16" s="12">
         <v>2030</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="12">
         <v>82</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>44256</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B17">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B17" s="12">
         <v>2030</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="12">
         <v>1050</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <v>44256</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B18">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18" s="12">
         <v>2030</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="12">
         <v>185</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <v>44256</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B19">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B19" s="12">
         <v>2030</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="12">
         <v>554</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <v>44256</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L19" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B20">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B20" s="12">
         <v>2030</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="12">
         <v>108</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <v>44256</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B21">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B21" s="12">
         <v>2030</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="12">
         <v>1025</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="13">
         <v>44256</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L21" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B22">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22" s="12">
         <v>2030</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="12">
         <v>130</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <v>44256</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="L22" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B23">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B23" s="12">
         <v>2030</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="12">
         <v>800</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="13">
         <v>44256</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="L23" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B24">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24" s="12">
         <v>2030</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="12">
         <v>52.5</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="13">
         <v>44256</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L24" s="12" t="s">
         <v>119</v>
       </c>
     </row>
